--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2722-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2722-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B948C2D-85C6-45BD-9A9F-D7B640BF9A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D9174D5-DEB2-4140-B3CF-087FCC79043C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{0EA98964-8ADE-4451-AB96-91B401476526}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{7F7A70B8-E515-432E-BFD3-577935E61F87}"/>
   </bookViews>
   <sheets>
     <sheet name="2722-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1457,26 +1457,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7EDD7A3-2613-4BD0-9177-951B39301414}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B07B58F4-B4EE-4544-A342-8BB07F2D814B}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1509,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1546,7 +1545,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1598,7 +1597,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1666,7 +1665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1738,7 +1737,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1810,7 +1809,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1882,7 +1881,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1954,7 +1953,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2098,7 +2097,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2170,7 +2169,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2242,7 +2241,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2386,7 +2385,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2458,7 +2457,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2530,7 +2529,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2602,7 +2601,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2674,7 +2673,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2746,7 +2745,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2818,7 +2817,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>44</v>
       </c>
